--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -751,7 +751,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1079,10 +1079,8 @@
           <t>Kritina Shrestha</t>
         </is>
       </c>
-      <c r="O2" s="3" t="inlineStr">
-        <is>
-          <t>9849747491</t>
-        </is>
+      <c r="O2" s="3" t="n">
+        <v>9849747491</v>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
@@ -1097,10 +1095,8 @@
       </c>
       <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr"/>
-      <c r="U2" s="3" t="inlineStr">
-        <is>
-          <t>9849747491</t>
-        </is>
+      <c r="U2" s="3" t="n">
+        <v>9849747491</v>
       </c>
       <c r="V2" s="3" t="inlineStr">
         <is>
@@ -1117,10 +1113,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y2" s="3" t="inlineStr">
-        <is>
-          <t>27.64397</t>
-        </is>
+      <c r="Y2" s="3" t="n">
+        <v>27.64397</v>
       </c>
       <c r="Z2" s="3" t="inlineStr">
         <is>
@@ -1172,25 +1166,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN2" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN2" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO2" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP2" s="3" t="inlineStr">
-        <is>
-          <t>85.33875</t>
-        </is>
+      <c r="AP2" s="3" t="n">
+        <v>85.33875</v>
       </c>
       <c r="AQ2" s="3" t="inlineStr"/>
       <c r="AR2" s="3" t="inlineStr">
         <is>
-          <t>Case : Iptv issue   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS2" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -532,14 +532,14 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -572,10 +572,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -612,23 +612,46 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>IPTV Issue</t>
+          <t>General / Other Issues</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>0.0%</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>100.0%</t>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -675,10 +698,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -688,10 +711,10 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -705,18 +728,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX2"/>
+  <dimension ref="A1:AX3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="23" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="19" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
@@ -739,10 +762,10 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="22" customWidth="1" min="32" max="32"/>
+    <col width="23" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
-    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
@@ -751,12 +774,12 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
     <col width="45" customWidth="1" min="48" max="48"/>
-    <col width="20" customWidth="1" min="49" max="49"/>
+    <col width="25" customWidth="1" min="49" max="49"/>
     <col width="23" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
@@ -1214,6 +1237,222 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:05 AM</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>no light on the STB</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379169</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>Pragal Kc</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Pragal Kc</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>9841915176</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr"/>
+      <c r="R3" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:05:05 AM</t>
+        </is>
+      </c>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr"/>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>9841915176</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:29:57 PM</t>
+        </is>
+      </c>
+      <c r="W3" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:05:05 AM</t>
+        </is>
+      </c>
+      <c r="X3" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y3" s="3" t="inlineStr">
+        <is>
+          <t>27.669</t>
+        </is>
+      </c>
+      <c r="Z3" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA3" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC3" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD3" s="3" t="inlineStr"/>
+      <c r="AE3" s="3" t="inlineStr">
+        <is>
+          <t>Sisha Cafe With Fast Food,Ekatamarga 34, ???????? , Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF3" s="3" t="inlineStr">
+        <is>
+          <t>pragalrock@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG3" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB Adaptor damage Issue</t>
+        </is>
+      </c>
+      <c r="AH3" s="3" t="inlineStr"/>
+      <c r="AI3" s="3" t="inlineStr">
+        <is>
+          <t>16:36 hour</t>
+        </is>
+      </c>
+      <c r="AJ3" s="3" t="inlineStr"/>
+      <c r="AK3" s="3" t="inlineStr"/>
+      <c r="AL3" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>L24-7</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>85.34123</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr"/>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h 35m</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV3" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW3" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -774,7 +774,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1304,10 +1304,8 @@
           <t>Pragal Kc</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>9841915176</t>
-        </is>
+      <c r="O3" s="3" t="n">
+        <v>9841915176</v>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
@@ -1322,10 +1320,8 @@
       </c>
       <c r="S3" s="3" t="inlineStr"/>
       <c r="T3" s="3" t="inlineStr"/>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>9841915176</t>
-        </is>
+      <c r="U3" s="3" t="n">
+        <v>9841915176</v>
       </c>
       <c r="V3" s="3" t="inlineStr">
         <is>
@@ -1342,10 +1338,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y3" s="3" t="inlineStr">
-        <is>
-          <t>27.669</t>
-        </is>
+      <c r="Y3" s="3" t="n">
+        <v>27.669</v>
       </c>
       <c r="Z3" s="3" t="inlineStr">
         <is>
@@ -1401,25 +1395,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN3" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO3" s="3" t="inlineStr">
         <is>
           <t>L24-7</t>
         </is>
       </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>85.34123</t>
-        </is>
+      <c r="AP3" s="3" t="n">
+        <v>85.34123</v>
       </c>
       <c r="AQ3" s="3" t="inlineStr"/>
       <c r="AR3" s="3" t="inlineStr">
         <is>
-          <t>Case : no light on the STB  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS3" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -494,7 +494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -528,36 +528,54 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Shashikant Chaudhary</t>
+          <t>Sabin Giri</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>GRAND TOTAL (ALL TEAM)</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>50.0%</t>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -572,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -628,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -651,7 +669,30 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -666,12 +707,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -682,10 +724,15 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
@@ -698,23 +745,45 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="D2" s="6" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="4" t="n">
-        <v>2</v>
+      <c r="D4" s="4" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -728,7 +797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -768,13 +837,13 @@
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
     <col width="17" customWidth="1" min="37" max="37"/>
-    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="19" customWidth="1" min="38" max="38"/>
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1443,6 +1512,222 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:36 AM</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6 upgarde</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380004</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Chhechima Sherpa</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Chhechima Sherpa</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>9818607638</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr"/>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:36:01 AM</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr"/>
+      <c r="T4" s="3" t="inlineStr"/>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>9818607638</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 10:33:24 AM</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:36:01 AM</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y4" s="3" t="inlineStr">
+        <is>
+          <t>27.730383</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA4" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD4" s="3" t="inlineStr"/>
+      <c r="AE4" s="3" t="inlineStr">
+        <is>
+          <t>Hamro Momo Ganatantra chowk, Boudha-6, Kathmandu 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF4" s="3" t="inlineStr">
+        <is>
+          <t>9826750385@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG4" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH4" s="3" t="inlineStr"/>
+      <c r="AI4" s="3" t="inlineStr">
+        <is>
+          <t>10:03 hour</t>
+        </is>
+      </c>
+      <c r="AJ4" s="3" t="inlineStr"/>
+      <c r="AK4" s="3" t="inlineStr"/>
+      <c r="AL4" s="3" t="inlineStr">
+        <is>
+          <t>Shristi Shrestha</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>L55-4</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>85.359308</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr"/>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1d 2m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>2</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -757,33 +757,49 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B5" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="C5" s="4" t="n">
         <v>3</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -797,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -843,7 +859,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1579,10 +1595,8 @@
           <t>Chhechima Sherpa</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>9818607638</t>
-        </is>
+      <c r="O4" s="3" t="n">
+        <v>9818607638</v>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
@@ -1597,10 +1611,8 @@
       </c>
       <c r="S4" s="3" t="inlineStr"/>
       <c r="T4" s="3" t="inlineStr"/>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t>9818607638</t>
-        </is>
+      <c r="U4" s="3" t="n">
+        <v>9818607638</v>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
@@ -1617,10 +1629,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y4" s="3" t="inlineStr">
-        <is>
-          <t>27.730383</t>
-        </is>
+      <c r="Y4" s="3" t="n">
+        <v>27.730383</v>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
@@ -1676,47 +1686,43 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN4" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN4" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
           <t>L55-4</t>
         </is>
       </c>
-      <c r="AP4" s="3" t="inlineStr">
-        <is>
-          <t>85.359308</t>
-        </is>
+      <c r="AP4" s="3" t="n">
+        <v>85.359308</v>
       </c>
       <c r="AQ4" s="3" t="inlineStr"/>
       <c r="AR4" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>1d 2m</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>0m</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>1d 2m</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t>Completed (Completed)</t>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6 upgarde   has been updated by Sabin Giri</t>
-        </is>
-      </c>
       <c r="AW4" s="3" t="inlineStr">
         <is>
           <t>WiFi 6 Upgrade</t>
@@ -1725,6 +1731,114 @@
       <c r="AX4" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:59 AM</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr"/>
+      <c r="J5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="inlineStr"/>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr"/>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr"/>
+      <c r="T5" s="3" t="inlineStr"/>
+      <c r="U5" s="3" t="inlineStr"/>
+      <c r="V5" s="3" t="inlineStr"/>
+      <c r="W5" s="3" t="inlineStr"/>
+      <c r="X5" s="3" t="inlineStr"/>
+      <c r="Y5" s="3" t="inlineStr"/>
+      <c r="Z5" s="3" t="inlineStr"/>
+      <c r="AA5" s="3" t="inlineStr"/>
+      <c r="AB5" s="3" t="inlineStr"/>
+      <c r="AC5" s="3" t="inlineStr"/>
+      <c r="AD5" s="3" t="inlineStr"/>
+      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AF5" s="3" t="inlineStr"/>
+      <c r="AG5" s="3" t="inlineStr"/>
+      <c r="AH5" s="3" t="inlineStr"/>
+      <c r="AI5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="3" t="inlineStr"/>
+      <c r="AK5" s="3" t="inlineStr"/>
+      <c r="AL5" s="3" t="inlineStr"/>
+      <c r="AM5" s="3" t="inlineStr"/>
+      <c r="AN5" s="3" t="inlineStr"/>
+      <c r="AO5" s="3" t="inlineStr"/>
+      <c r="AP5" s="3" t="inlineStr"/>
+      <c r="AQ5" s="3" t="inlineStr"/>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (nan)</t>
+        </is>
+      </c>
+      <c r="AV5" s="3" t="inlineStr">
+        <is>
+          <t>Case : Iptv issue   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW5" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX5" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
         </is>
       </c>
     </row>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -741,46 +741,46 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>IPTV STB Adaptor damage Issue</t>
+          <t>Router Upgrade  Wi-Fi 6</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="n">
-        <v>2</v>
-      </c>
       <c r="D2" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB Adaptor damage Issue</t>
         </is>
       </c>
       <c r="B3" s="3" t="n">
         <v>0</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Router Upgrade  Wi-Fi 6</t>
+          <t>Other / Uncategorized</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>1</v>
@@ -793,13 +793,13 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>3</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -813,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AX7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -847,7 +847,7 @@
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="23" customWidth="1" min="32" max="32"/>
+    <col width="27" customWidth="1" min="32" max="32"/>
     <col width="32" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -859,7 +859,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1842,6 +1842,438 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06 AM</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379167</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Pandit</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Kamal Pandit</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>9846802439</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr"/>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:53 AM</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr"/>
+      <c r="T6" s="3" t="inlineStr"/>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>9846802439</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:27:43 PM</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:53 AM</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y6" s="3" t="inlineStr">
+        <is>
+          <t>27.72929</t>
+        </is>
+      </c>
+      <c r="Z6" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA6" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD6" s="3" t="inlineStr"/>
+      <c r="AE6" s="3" t="inlineStr">
+        <is>
+          <t>Near Tenzing ChowkKapan, Budhanilkantha 44600, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF6" s="3" t="inlineStr">
+        <is>
+          <t>kamalnature772@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG6" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH6" s="3" t="inlineStr"/>
+      <c r="AI6" s="3" t="inlineStr">
+        <is>
+          <t>17:39 hour</t>
+        </is>
+      </c>
+      <c r="AJ6" s="3" t="inlineStr"/>
+      <c r="AK6" s="3" t="inlineStr"/>
+      <c r="AL6" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>L50-4</t>
+        </is>
+      </c>
+      <c r="AP6" s="3" t="inlineStr">
+        <is>
+          <t>85.360844</t>
+        </is>
+      </c>
+      <c r="AQ6" s="3" t="inlineStr"/>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 39m</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV6" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW6" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX6" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06 AM</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wfi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>wfi6</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379187</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>Dhijan Dahal</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>Dhijan Dahal</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
+        <is>
+          <t>9862910031</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr"/>
+      <c r="R7" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:24 AM</t>
+        </is>
+      </c>
+      <c r="S7" s="3" t="inlineStr"/>
+      <c r="T7" s="3" t="inlineStr"/>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>9862910031</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:44:30 PM</t>
+        </is>
+      </c>
+      <c r="W7" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:06:24 AM</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t>27.734268</t>
+        </is>
+      </c>
+      <c r="Z7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA7" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC7" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD7" s="3" t="inlineStr"/>
+      <c r="AE7" s="3" t="inlineStr">
+        <is>
+          <t>Kapan Near  Trinetra Vidhya Niketan., Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF7" s="3" t="inlineStr">
+        <is>
+          <t>dhijandahal1@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG7" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH7" s="3" t="inlineStr"/>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>17:22 hour</t>
+        </is>
+      </c>
+      <c r="AJ7" s="3" t="inlineStr"/>
+      <c r="AK7" s="3" t="inlineStr"/>
+      <c r="AL7" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO7" s="3" t="inlineStr">
+        <is>
+          <t>L4-2</t>
+        </is>
+      </c>
+      <c r="AP7" s="3" t="inlineStr">
+        <is>
+          <t>85.353543</t>
+        </is>
+      </c>
+      <c r="AQ7" s="3" t="inlineStr"/>
+      <c r="AR7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wfi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS7" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT7" s="3" t="inlineStr">
+        <is>
+          <t>1d 21h 21m</t>
+        </is>
+      </c>
+      <c r="AU7" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV7" s="3" t="inlineStr">
+        <is>
+          <t>Case : wfi6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW7" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX7" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -859,7 +859,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -1899,20 +1899,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>Kamal Pandit</t>
         </is>
       </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>9846802439</t>
-        </is>
+      <c r="O6" s="3" t="n">
+        <v>9846802439</v>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
@@ -1927,10 +1921,8 @@
       </c>
       <c r="S6" s="3" t="inlineStr"/>
       <c r="T6" s="3" t="inlineStr"/>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>9846802439</t>
-        </is>
+      <c r="U6" s="3" t="n">
+        <v>9846802439</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -1947,10 +1939,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y6" s="3" t="inlineStr">
-        <is>
-          <t>27.72929</t>
-        </is>
+      <c r="Y6" s="3" t="n">
+        <v>27.72929</v>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
@@ -2006,25 +1996,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN6" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
           <t>L50-4</t>
         </is>
       </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>85.360844</t>
-        </is>
+      <c r="AP6" s="3" t="n">
+        <v>85.360844</v>
       </c>
       <c r="AQ6" s="3" t="inlineStr"/>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
@@ -2115,20 +2101,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="3" t="inlineStr">
         <is>
           <t>Dhijan Dahal</t>
         </is>
       </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>9862910031</t>
-        </is>
+      <c r="O7" s="3" t="n">
+        <v>9862910031</v>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
@@ -2143,10 +2123,8 @@
       </c>
       <c r="S7" s="3" t="inlineStr"/>
       <c r="T7" s="3" t="inlineStr"/>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t>9862910031</t>
-        </is>
+      <c r="U7" s="3" t="n">
+        <v>9862910031</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -2163,10 +2141,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
-          <t>27.734268</t>
-        </is>
+      <c r="Y7" s="3" t="n">
+        <v>27.734268</v>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -2222,25 +2198,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN7" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
           <t>L4-2</t>
         </is>
       </c>
-      <c r="AP7" s="3" t="inlineStr">
-        <is>
-          <t>85.353543</t>
-        </is>
+      <c r="AP7" s="3" t="n">
+        <v>85.353543</v>
       </c>
       <c r="AQ7" s="3" t="inlineStr"/>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>Case : wfi6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -773,7 +773,7 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Other / Uncategorized</t>
+          <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
       <c r="B4" s="3" t="n">
@@ -787,19 +787,35 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Other / Uncategorized</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>6</v>
+      <c r="C6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -813,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX7"/>
+  <dimension ref="A1:AX8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -836,13 +852,13 @@
     <col width="26" customWidth="1" min="18" max="18"/>
     <col width="37" customWidth="1" min="19" max="19"/>
     <col width="37" customWidth="1" min="20" max="20"/>
-    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
-    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
@@ -859,7 +875,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2246,6 +2262,218 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:43 AM</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>no light blinking</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379325</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Sanu Maya Tamang</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Sanu Maya Tamang</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>9849576316</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr"/>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:43:41 AM</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr"/>
+      <c r="T8" s="3" t="inlineStr"/>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>BKT9849576316</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 03:42:44 PM</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 11:43:41 AM</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr"/>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
+          <t>Hardware Damage / Malfunction</t>
+        </is>
+      </c>
+      <c r="AA8" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC8" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr"/>
+      <c r="AE8" s="3" t="inlineStr">
+        <is>
+          <t>27.69646053946493, 85.37977494133595, Bhaktapur, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF8" s="3" t="inlineStr">
+        <is>
+          <t>9849576316@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG8" s="3" t="inlineStr">
+        <is>
+          <t>IPTV STB box Damage Issue</t>
+        </is>
+      </c>
+      <c r="AH8" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>16:01 hour</t>
+        </is>
+      </c>
+      <c r="AJ8" s="3" t="inlineStr"/>
+      <c r="AK8" s="3" t="inlineStr"/>
+      <c r="AL8" s="3" t="inlineStr">
+        <is>
+          <t>Manisha kunwar</t>
+        </is>
+      </c>
+      <c r="AM8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN8" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO8" s="3" t="inlineStr">
+        <is>
+          <t>L52-7</t>
+        </is>
+      </c>
+      <c r="AP8" s="3" t="inlineStr"/>
+      <c r="AQ8" s="3" t="inlineStr"/>
+      <c r="AR8" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS8" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT8" s="3" t="inlineStr">
+        <is>
+          <t>1d 20h</t>
+        </is>
+      </c>
+      <c r="AU8" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV8" s="3" t="inlineStr">
+        <is>
+          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW8" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX8" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -875,7 +875,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2329,10 +2329,8 @@
           <t>Sanu Maya Tamang</t>
         </is>
       </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>9849576316</t>
-        </is>
+      <c r="O8" s="3" t="n">
+        <v>9849576316</v>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
@@ -2404,10 +2402,8 @@
           <t>IPTV STB box Damage Issue</t>
         </is>
       </c>
-      <c r="AH8" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH8" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
@@ -2426,10 +2422,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN8" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN8" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
@@ -2440,7 +2434,7 @@
       <c r="AQ8" s="3" t="inlineStr"/>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>Case : no light blinking   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>75.0%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>37.5%</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -707,10 +707,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="23" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -803,19 +803,35 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B7" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>7</v>
+      <c r="C7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -829,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX8"/>
+  <dimension ref="A1:AX9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -840,12 +856,12 @@
     <col width="17" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="32" customWidth="1" min="16" max="16"/>
     <col width="19" customWidth="1" min="17" max="17"/>
@@ -864,7 +880,7 @@
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
     <col width="27" customWidth="1" min="32" max="32"/>
-    <col width="32" customWidth="1" min="33" max="33"/>
+    <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
     <col width="17" customWidth="1" min="36" max="36"/>
@@ -875,7 +891,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2468,6 +2484,218 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:18 PM</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr"/>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>error 1400 issue in iptv</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379645</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>delight outsource security serves pvt</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
+          <t>delight outsource security serves pvt</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="inlineStr">
+        <is>
+          <t>9801887031</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr"/>
+      <c r="R9" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:18:27 PM</t>
+        </is>
+      </c>
+      <c r="S9" s="3" t="inlineStr"/>
+      <c r="T9" s="3" t="inlineStr"/>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>BKT9801877031</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 07:31:56 PM</t>
+        </is>
+      </c>
+      <c r="W9" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:18:27 PM</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr"/>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA9" s="3" t="inlineStr">
+        <is>
+          <t>Layer 2-CG Group</t>
+        </is>
+      </c>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC9" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD9" s="3" t="inlineStr"/>
+      <c r="AE9" s="3" t="inlineStr">
+        <is>
+          <t>HALESI MART PVT. LTD - Convenience store Manohara park Madhyapur Thimi 44600, Bhaktapur, Nepal, Nepa</t>
+        </is>
+      </c>
+      <c r="AF9" s="3" t="inlineStr">
+        <is>
+          <t>9851236610@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG9" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="AH9" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>12:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ9" s="3" t="inlineStr"/>
+      <c r="AK9" s="3" t="inlineStr"/>
+      <c r="AL9" s="3" t="inlineStr">
+        <is>
+          <t>Salbin Ghale</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>L58-8</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr"/>
+      <c r="AQ9" s="3" t="inlineStr"/>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 46m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
+          <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
     </row>
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>44.4%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
     </row>
@@ -748,10 +748,10 @@
         <v>3</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -828,10 +828,10 @@
         <v>3</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX9"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -2551,10 +2551,8 @@
           <t>delight outsource security serves pvt</t>
         </is>
       </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>9801887031</t>
-        </is>
+      <c r="O9" s="3" t="n">
+        <v>9801887031</v>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
@@ -2626,10 +2624,8 @@
           <t>SKYCOM-No internet connection on STB</t>
         </is>
       </c>
-      <c r="AH9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="AH9" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
@@ -2648,10 +2644,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN9" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
@@ -2662,35 +2656,251 @@
       <c r="AQ9" s="3" t="inlineStr"/>
       <c r="AR9" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>1d 16h 46m</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV9" s="3" t="inlineStr">
+        <is>
           <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AS9" s="3" t="inlineStr">
+      <c r="AW9" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX9" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:43 PM</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>router upgrade</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379467</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>Manoj Karanjit</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Manoj Karanjit</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>9841348904</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr"/>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:43:39 PM</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr"/>
+      <c r="T10" s="3" t="inlineStr"/>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>9860976151</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 05:02:06 PM</t>
+        </is>
+      </c>
+      <c r="W10" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 12:43:39 PM</t>
+        </is>
+      </c>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y10" s="3" t="inlineStr">
+        <is>
+          <t>27.68287</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA10" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC10" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD10" s="3" t="inlineStr"/>
+      <c r="AE10" s="3" t="inlineStr">
+        <is>
+          <t>Near The Burger house and crunchy fried chicken (Gatthaghar), Madhyapur Thimi , Bagmati, Central, Ne</t>
+        </is>
+      </c>
+      <c r="AF10" s="3" t="inlineStr">
+        <is>
+          <t>karanjitmanoj@yahoo.com</t>
+        </is>
+      </c>
+      <c r="AG10" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH10" s="3" t="inlineStr"/>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>15:41 hour</t>
+        </is>
+      </c>
+      <c r="AJ10" s="3" t="inlineStr"/>
+      <c r="AK10" s="3" t="inlineStr"/>
+      <c r="AL10" s="3" t="inlineStr">
+        <is>
+          <t>Rejina Shrestha</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>3,2</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>85.3856</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3" t="inlineStr"/>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>1d 16h 46m</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>1d 19h 41m</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV9" s="3" t="inlineStr">
-        <is>
-          <t>Case : error 1400 issue in iptv  has been updated by Shashikant Chaudhary</t>
-        </is>
-      </c>
-      <c r="AW9" s="3" t="inlineStr">
-        <is>
-          <t>IPTV Issue</t>
-        </is>
-      </c>
-      <c r="AX9" s="3" t="inlineStr">
+      <c r="AV10" s="3" t="inlineStr">
+        <is>
+          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW10" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX10" s="3" t="inlineStr">
         <is>
           <t>Shashikant Chaudhary</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -891,7 +891,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2747,20 +2747,14 @@
           <t>Completed</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>Manoj Karanjit</t>
         </is>
       </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>9841348904</t>
-        </is>
+      <c r="O10" s="3" t="n">
+        <v>9841348904</v>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
@@ -2795,10 +2789,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y10" s="3" t="inlineStr">
-        <is>
-          <t>27.68287</t>
-        </is>
+      <c r="Y10" s="3" t="n">
+        <v>27.68287</v>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
@@ -2854,25 +2846,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN10" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
           <t>3,2</t>
         </is>
       </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>85.3856</t>
-        </is>
+      <c r="AP10" s="3" t="n">
+        <v>85.3856</v>
       </c>
       <c r="AQ10" s="3" t="inlineStr"/>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>Case : router upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>80.0%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>40.0%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>20.0%</t>
         </is>
       </c>
     </row>
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>30.0%</t>
         </is>
       </c>
     </row>
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX10"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -891,7 +891,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2894,6 +2894,222 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 1:22 PM</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr"/>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380358</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>Yashu Karki</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>Yashu Karki</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t>9841840682</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr"/>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:22:39 PM</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr"/>
+      <c r="T11" s="3" t="inlineStr"/>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>9841840682</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 02:35:28 PM</t>
+        </is>
+      </c>
+      <c r="W11" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:22:39 PM</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t>27.73707</t>
+        </is>
+      </c>
+      <c r="Z11" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA11" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr"/>
+      <c r="AE11" s="3" t="inlineStr">
+        <is>
+          <t>Maharajung, Kanti Sangam Marg, Next to Holy Bell Girls Hostel Maharajgunj, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF11" s="3" t="inlineStr">
+        <is>
+          <t>blitzshreya@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG11" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH11" s="3" t="inlineStr"/>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>08:47 hour</t>
+        </is>
+      </c>
+      <c r="AJ11" s="3" t="inlineStr"/>
+      <c r="AK11" s="3" t="inlineStr"/>
+      <c r="AL11" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO11" s="3" t="inlineStr">
+        <is>
+          <t>L36-3</t>
+        </is>
+      </c>
+      <c r="AP11" s="3" t="inlineStr">
+        <is>
+          <t>85.32845</t>
+        </is>
+      </c>
+      <c r="AQ11" s="3" t="inlineStr"/>
+      <c r="AR11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS11" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT11" s="3" t="inlineStr">
+        <is>
+          <t>22h 47m</t>
+        </is>
+      </c>
+      <c r="AU11" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV11" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW11" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX11" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -891,7 +891,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -2961,10 +2961,8 @@
           <t>Yashu Karki</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t>9841840682</t>
-        </is>
+      <c r="O11" s="3" t="n">
+        <v>9841840682</v>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
@@ -2999,10 +2997,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t>27.73707</t>
-        </is>
+      <c r="Y11" s="3" t="n">
+        <v>27.73707</v>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -3058,25 +3054,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN11" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
           <t>L36-3</t>
         </is>
       </c>
-      <c r="AP11" s="3" t="inlineStr">
-        <is>
-          <t>85.32845</t>
-        </is>
+      <c r="AP11" s="3" t="n">
+        <v>85.32845</v>
       </c>
       <c r="AQ11" s="3" t="inlineStr"/>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>81.8%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
     </row>
@@ -680,10 +680,10 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
@@ -692,7 +692,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>36.4%</t>
         </is>
       </c>
     </row>
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX11"/>
+  <dimension ref="A1:AX12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -891,7 +891,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3102,6 +3102,222 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 1:49 PM</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379202</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>Nabin Paudel</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Nabin Paudel</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>9840056783</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr"/>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:49:26 PM</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr"/>
+      <c r="T12" s="3" t="inlineStr"/>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>9840056783</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 01:53:02 PM</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 01:49:26 PM</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y12" s="3" t="inlineStr">
+        <is>
+          <t>27.7322</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA12" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC12" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr"/>
+      <c r="AE12" s="3" t="inlineStr">
+        <is>
+          <t>Sukedhara , Nilo Pul, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF12" s="3" t="inlineStr">
+        <is>
+          <t>nabin78paudel@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG12" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH12" s="3" t="inlineStr"/>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>19:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ12" s="3" t="inlineStr"/>
+      <c r="AK12" s="3" t="inlineStr"/>
+      <c r="AL12" s="3" t="inlineStr">
+        <is>
+          <t>Monika Chaudhary</t>
+        </is>
+      </c>
+      <c r="AM12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN12" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO12" s="3" t="inlineStr">
+        <is>
+          <t>L6-6</t>
+        </is>
+      </c>
+      <c r="AP12" s="3" t="inlineStr">
+        <is>
+          <t>85.35031</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3" t="inlineStr"/>
+      <c r="AR12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 56m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>83.3%</t>
         </is>
       </c>
     </row>
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>16.7%</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
     </row>
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>1</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>6</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -3169,10 +3169,8 @@
           <t>Nabin Paudel</t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t>9840056783</t>
-        </is>
+      <c r="O12" s="3" t="n">
+        <v>9840056783</v>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
@@ -3207,10 +3205,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y12" s="3" t="inlineStr">
-        <is>
-          <t>27.7322</t>
-        </is>
+      <c r="Y12" s="3" t="n">
+        <v>27.7322</v>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
@@ -3266,53 +3262,265 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN12" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN12" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
           <t>L6-6</t>
         </is>
       </c>
-      <c r="AP12" s="3" t="inlineStr">
-        <is>
-          <t>85.35031</t>
-        </is>
+      <c r="AP12" s="3" t="n">
+        <v>85.35030999999999</v>
       </c>
       <c r="AQ12" s="3" t="inlineStr"/>
       <c r="AR12" s="3" t="inlineStr">
         <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="AS12" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT12" s="3" t="inlineStr">
+        <is>
+          <t>1d 23h 56m</t>
+        </is>
+      </c>
+      <c r="AU12" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV12" s="3" t="inlineStr">
+        <is>
           <t>Case : wifi 6  has been updated by Sabin Giri</t>
         </is>
       </c>
-      <c r="AS12" s="3" t="inlineStr">
+      <c r="AW12" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX12" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 2:10 PM</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr"/>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Call back  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Call back</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>TKT1274645</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>Sakar Giri</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>Sakar Giri</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>9841864340</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr"/>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:10:10 PM</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr"/>
+      <c r="T13" s="3" t="inlineStr"/>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>9841864340</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>26 Jul 2026 02:49:04 PM</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:10:10 PM</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y13" s="3" t="inlineStr">
+        <is>
+          <t>27.73427</t>
+        </is>
+      </c>
+      <c r="Z13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA13" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD13" s="3" t="inlineStr"/>
+      <c r="AE13" s="3" t="inlineStr">
+        <is>
+          <t>Kathmandu Budhanilkantha Kapan ward no:11 kharibot near Kapan,kharibot ani gumba, Bagmati, Central,</t>
+        </is>
+      </c>
+      <c r="AF13" s="3" t="inlineStr">
+        <is>
+          <t>sakargiri99@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG13" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH13" s="3" t="inlineStr"/>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>12:10 hour</t>
+        </is>
+      </c>
+      <c r="AJ13" s="3" t="inlineStr"/>
+      <c r="AK13" s="3" t="inlineStr"/>
+      <c r="AL13" s="3" t="inlineStr">
+        <is>
+          <t>Kusum Gurung</t>
+        </is>
+      </c>
+      <c r="AM13" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>L35-1</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>85.35373</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr"/>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Call back  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
         <is>
           <t>0m</t>
         </is>
       </c>
-      <c r="AT12" s="3" t="inlineStr">
-        <is>
-          <t>1d 23h 56m</t>
-        </is>
-      </c>
-      <c r="AU12" s="3" t="inlineStr">
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>93d 23h 21m</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
         <is>
           <t>Completed (Completed)</t>
         </is>
       </c>
-      <c r="AV12" s="3" t="inlineStr">
-        <is>
-          <t>Case : wifi 6  has been updated by Sabin Giri</t>
-        </is>
-      </c>
-      <c r="AW12" s="3" t="inlineStr">
-        <is>
-          <t>WiFi 6 Upgrade</t>
-        </is>
-      </c>
-      <c r="AX12" s="3" t="inlineStr">
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>Case : Call back  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
         <is>
           <t>Sabin Giri</t>
         </is>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -891,7 +891,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3377,10 +3377,8 @@
           <t>Sakar Giri</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>9841864340</t>
-        </is>
+      <c r="O13" s="3" t="n">
+        <v>9841864340</v>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
@@ -3415,10 +3413,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y13" s="3" t="inlineStr">
-        <is>
-          <t>27.73427</t>
-        </is>
+      <c r="Y13" s="3" t="n">
+        <v>27.73427</v>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
@@ -3474,25 +3470,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN13" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN13" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
           <t>L35-1</t>
         </is>
       </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>85.35373</t>
-        </is>
+      <c r="AP13" s="3" t="n">
+        <v>85.35373</v>
       </c>
       <c r="AQ13" s="3" t="inlineStr"/>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>Case : Call back  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -532,10 +532,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>38.5%</t>
         </is>
       </c>
     </row>
@@ -657,19 +657,19 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -805,33 +805,49 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>12</v>
+      <c r="D8" s="4" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -845,7 +861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX13"/>
+  <dimension ref="A1:AX14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -891,7 +907,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3518,6 +3534,218 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 2:52 PM</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>WGnmUJF06LTlUriJ5DeDBQ==</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV buffering issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>IPTV buffering issue</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380264</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>Nirmala Gurung</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>Nirmala Gurung</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t>9818606881</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr"/>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:52:31 PM</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>9818606881</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 01:25:24 PM</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 02:52:31 PM</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t>27.744901</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Related Issues</t>
+        </is>
+      </c>
+      <c r="AA14" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC14" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr"/>
+      <c r="AE14" s="3" t="inlineStr">
+        <is>
+          <t>Duda nilakanth, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF14" s="3" t="inlineStr"/>
+      <c r="AG14" s="3" t="inlineStr">
+        <is>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
+        </is>
+      </c>
+      <c r="AH14" s="3" t="inlineStr"/>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>11:27 hour</t>
+        </is>
+      </c>
+      <c r="AJ14" s="3" t="inlineStr"/>
+      <c r="AK14" s="3" t="inlineStr"/>
+      <c r="AL14" s="3" t="inlineStr">
+        <is>
+          <t>Sanish Magar</t>
+        </is>
+      </c>
+      <c r="AM14" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AN14" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO14" s="3" t="inlineStr">
+        <is>
+          <t>L27-7</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>85.36259</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr"/>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV buffering issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT14" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 27m</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV14" s="3" t="inlineStr">
+        <is>
+          <t>Case : IPTV buffering issue  has been updated by Sabin Giri</t>
+        </is>
+      </c>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>IPTV Issue</t>
+        </is>
+      </c>
+      <c r="AX14" s="3" t="inlineStr">
+        <is>
+          <t>Sabin Giri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -907,7 +907,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="12" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3601,10 +3601,8 @@
           <t>Nirmala Gurung</t>
         </is>
       </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>9818606881</t>
-        </is>
+      <c r="O14" s="3" t="n">
+        <v>9818606881</v>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
@@ -3639,10 +3637,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t>27.744901</t>
-        </is>
+      <c r="Y14" s="3" t="n">
+        <v>27.744901</v>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
@@ -3694,25 +3690,21 @@
           <t>Sabin Giri</t>
         </is>
       </c>
-      <c r="AN14" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN14" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
           <t>L27-7</t>
         </is>
       </c>
-      <c r="AP14" s="3" t="inlineStr">
-        <is>
-          <t>85.36259</t>
-        </is>
+      <c r="AP14" s="3" t="n">
+        <v>85.36259</v>
       </c>
       <c r="AQ14" s="3" t="inlineStr"/>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>Case : IPTV buffering issue  has been updated by Sabin Giri</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -550,14 +550,14 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>57.1%</t>
         </is>
       </c>
     </row>
@@ -568,14 +568,14 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>71.4%</t>
         </is>
       </c>
     </row>
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
@@ -646,7 +646,7 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>28.6%</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>14.3%</t>
         </is>
       </c>
     </row>
@@ -680,19 +680,19 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>52.4%</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -748,10 +748,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
@@ -805,14 +805,14 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-Channel buffering,feeze issue</t>
+          <t>Router Upgrade Dual Band</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>1</v>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>1</v>
@@ -821,33 +821,49 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>SKYCOM-No internet connection on STB</t>
+          <t>SKYCOM-Channel buffering,feeze issue</t>
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>0</v>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>1</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>SKYCOM-No internet connection on STB</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
         <is>
           <t>Grand Total</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D8" s="4" t="n">
-        <v>13</v>
+      <c r="C9" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -861,7 +877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX14"/>
+  <dimension ref="A1:AX22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
@@ -888,14 +904,14 @@
     <col width="26" customWidth="1" min="22" max="22"/>
     <col width="26" customWidth="1" min="23" max="23"/>
     <col width="29" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
     <col width="32" customWidth="1" min="26" max="26"/>
     <col width="19" customWidth="1" min="27" max="27"/>
     <col width="17" customWidth="1" min="28" max="28"/>
     <col width="12" customWidth="1" min="29" max="29"/>
     <col width="12" customWidth="1" min="30" max="30"/>
     <col width="45" customWidth="1" min="31" max="31"/>
-    <col width="27" customWidth="1" min="32" max="32"/>
+    <col width="31" customWidth="1" min="32" max="32"/>
     <col width="39" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
     <col width="13" customWidth="1" min="35" max="35"/>
@@ -905,9 +921,9 @@
     <col width="23" customWidth="1" min="39" max="39"/>
     <col width="28" customWidth="1" min="40" max="40"/>
     <col width="27" customWidth="1" min="41" max="41"/>
-    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="34" customWidth="1" min="44" max="44"/>
+    <col width="45" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3738,6 +3754,1698 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:16 PM</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr"/>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381041</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>Digam Kumar Rana</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>Digam Kumar Rana</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t>9702683606</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr"/>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:16:18 PM</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>9810214387</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 10:17:30 AM</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:16:18 PM</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y15" s="3" t="inlineStr">
+        <is>
+          <t>27.6553579</t>
+        </is>
+      </c>
+      <c r="Z15" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA15" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB15" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr"/>
+      <c r="AE15" s="3" t="inlineStr">
+        <is>
+          <t>Buddha Party Palace,Tikathali, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF15" s="3" t="inlineStr">
+        <is>
+          <t>zarusmagar@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG15" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH15" s="3" t="inlineStr"/>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>06:59 hour</t>
+        </is>
+      </c>
+      <c r="AJ15" s="3" t="inlineStr"/>
+      <c r="AK15" s="3" t="inlineStr"/>
+      <c r="AL15" s="3" t="inlineStr">
+        <is>
+          <t>Indra KC</t>
+        </is>
+      </c>
+      <c r="AM15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN15" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO15" s="3" t="inlineStr">
+        <is>
+          <t>4,12</t>
+        </is>
+      </c>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>85.3559794</t>
+        </is>
+      </c>
+      <c r="AQ15" s="3" t="inlineStr"/>
+      <c r="AR15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS15" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT15" s="3" t="inlineStr">
+        <is>
+          <t>6h 58m</t>
+        </is>
+      </c>
+      <c r="AU15" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV15" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW15" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX15" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:09 PM</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>wifi 6</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380806</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>Aayush shrestha</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>Aayush shrestha</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr">
+        <is>
+          <t>9843468465</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr"/>
+      <c r="R16" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 09:07:13 PM</t>
+        </is>
+      </c>
+      <c r="S16" s="3" t="inlineStr"/>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>9843468465</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 09:07:13 PM</t>
+        </is>
+      </c>
+      <c r="W16" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:09:00 PM</t>
+        </is>
+      </c>
+      <c r="X16" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y16" s="3" t="inlineStr">
+        <is>
+          <t>27.67349</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA16" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC16" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr"/>
+      <c r="AE16" s="3" t="inlineStr">
+        <is>
+          <t>Bhaktapur, ghatthaghar near by nepal telecom, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF16" s="3" t="inlineStr">
+        <is>
+          <t>aayushsth77@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG16" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH16" s="3" t="inlineStr"/>
+      <c r="AI16" s="3" t="inlineStr"/>
+      <c r="AJ16" s="3" t="inlineStr"/>
+      <c r="AK16" s="3" t="inlineStr"/>
+      <c r="AL16" s="3" t="inlineStr">
+        <is>
+          <t>Aakash Shah</t>
+        </is>
+      </c>
+      <c r="AM16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO16" s="3" t="inlineStr">
+        <is>
+          <t>L51-6</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>85.37342</t>
+        </is>
+      </c>
+      <c r="AQ16" s="3" t="inlineStr"/>
+      <c r="AR16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS16" s="3" t="inlineStr">
+        <is>
+          <t>20h 1m</t>
+        </is>
+      </c>
+      <c r="AT16" s="3" t="inlineStr">
+        <is>
+          <t>20h 1m</t>
+        </is>
+      </c>
+      <c r="AU16" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV16" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW16" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX16" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:07 PM</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>TKT1381003</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>Riwaz Thapa</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>Riwaz Thapa</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr">
+        <is>
+          <t>9843819136</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr"/>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 09:44:42 AM</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr"/>
+      <c r="T17" s="3" t="inlineStr"/>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>BKT9843819136</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 09:44:42 AM</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:07:28 PM</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y17" s="3" t="inlineStr"/>
+      <c r="Z17" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA17" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC17" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr"/>
+      <c r="AE17" s="3" t="inlineStr">
+        <is>
+          <t>Marigold E.B. School - School merigold english boarding school balkot,bhaktapur,near 32701, Bagmati,</t>
+        </is>
+      </c>
+      <c r="AF17" s="3" t="inlineStr">
+        <is>
+          <t>9841479321@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG17" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH17" s="3" t="inlineStr"/>
+      <c r="AI17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="3" t="inlineStr"/>
+      <c r="AK17" s="3" t="inlineStr"/>
+      <c r="AL17" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>L21-6</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr"/>
+      <c r="AQ17" s="3" t="inlineStr"/>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>7h 22m</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>7h 22m</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV17" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW17" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX17" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:06 PM</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6 upgrade</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380906</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Anjali Khadka</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>Anjali Khadka</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>9813192017</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr"/>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 08:02:33 AM</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr"/>
+      <c r="T18" s="3" t="inlineStr"/>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>9813286073</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 08:02:33 AM</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:06:46 PM</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y18" s="3" t="inlineStr">
+        <is>
+          <t>27.667993</t>
+        </is>
+      </c>
+      <c r="Z18" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA18" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC18" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD18" s="3" t="inlineStr"/>
+      <c r="AE18" s="3" t="inlineStr">
+        <is>
+          <t>Balkot, Brihaspati Marg -2, Bagmati, Nepal, Nepal</t>
+        </is>
+      </c>
+      <c r="AF18" s="3" t="inlineStr">
+        <is>
+          <t>khadkaanjuli1998@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG18" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH18" s="3" t="inlineStr"/>
+      <c r="AI18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="3" t="inlineStr"/>
+      <c r="AK18" s="3" t="inlineStr"/>
+      <c r="AL18" s="3" t="inlineStr">
+        <is>
+          <t>Merika Silwal</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>85.368072</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr"/>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>9h 4m</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>9h 4m</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV18" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW18" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX18" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:06 PM</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>wifi6</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379390</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>Prashant Ulak</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>On Hold</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>Prashant Ulak</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>9861691382</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr"/>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:27:35 PM</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr"/>
+      <c r="T19" s="3" t="inlineStr"/>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>9861691382</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:27:35 PM</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:06:03 PM</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>27.6781</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA19" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB19" s="3" t="inlineStr">
+        <is>
+          <t>Laxman Koirala</t>
+        </is>
+      </c>
+      <c r="AC19" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD19" s="3" t="inlineStr"/>
+      <c r="AE19" s="3" t="inlineStr">
+        <is>
+          <t>61 koteshwor sky bridge, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF19" s="3" t="inlineStr">
+        <is>
+          <t>prashant9843215397@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG19" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH19" s="3" t="inlineStr"/>
+      <c r="AI19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="3" t="inlineStr"/>
+      <c r="AK19" s="3" t="inlineStr"/>
+      <c r="AL19" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>85.34772</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr"/>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>2d 38m</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>2d 38m</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t>Other / In Progress (On Hold)</t>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:04 PM</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Wifi 6</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380633</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Anurag Karki</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>Anurag Karki</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr">
+        <is>
+          <t>9861095557</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q20" s="3" t="inlineStr"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:04:56 PM</t>
+        </is>
+      </c>
+      <c r="S20" s="3" t="inlineStr"/>
+      <c r="T20" s="3" t="inlineStr"/>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>BKT9861095557</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 06:12:47 PM</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:04:56 PM</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y20" s="3" t="inlineStr"/>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA20" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC20" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD20" s="3" t="inlineStr"/>
+      <c r="AE20" s="3" t="inlineStr">
+        <is>
+          <t>Public Health Office Bhaktapur - Government office MC74+4PG Unnamed Road Suryabinayak 44800  , Bhakt</t>
+        </is>
+      </c>
+      <c r="AF20" s="3" t="inlineStr">
+        <is>
+          <t>anuragkarki6@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG20" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH20" s="3" t="inlineStr"/>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>08:52 hour</t>
+        </is>
+      </c>
+      <c r="AJ20" s="3" t="inlineStr"/>
+      <c r="AK20" s="3" t="inlineStr"/>
+      <c r="AL20" s="3" t="inlineStr">
+        <is>
+          <t>Nirajan Dhamala</t>
+        </is>
+      </c>
+      <c r="AM20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN20" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO20" s="3" t="inlineStr">
+        <is>
+          <t>L10-3</t>
+        </is>
+      </c>
+      <c r="AP20" s="3" t="inlineStr"/>
+      <c r="AQ20" s="3" t="inlineStr"/>
+      <c r="AR20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS20" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT20" s="3" t="inlineStr">
+        <is>
+          <t>22h 52m</t>
+        </is>
+      </c>
+      <c r="AU20" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV20" s="3" t="inlineStr">
+        <is>
+          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW20" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX20" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:04 PM</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>router change</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>TKT1379373</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Kumar Regmi</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>Ramesh Kumar Regmi</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>9811566677</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr"/>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:04:01 PM</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr"/>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>9811566677</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>26 Oct 2026 04:20:05 PM</t>
+        </is>
+      </c>
+      <c r="W21" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:04:01 PM</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>27.69851</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA21" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC21" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD21" s="3" t="inlineStr"/>
+      <c r="AE21" s="3" t="inlineStr">
+        <is>
+          <t>Basuki Marga, Ghumnti Kumari Marga, Near To Rabindra Cold Store &amp; Nepal investment and Securities Tr</t>
+        </is>
+      </c>
+      <c r="AF21" s="3" t="inlineStr">
+        <is>
+          <t>regmi48ramesh@gmail.com</t>
+        </is>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade Dual Band</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr"/>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>20:44 hour</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr"/>
+      <c r="AK21" s="3" t="inlineStr"/>
+      <c r="AL21" s="3" t="inlineStr">
+        <is>
+          <t>Swastima Silwal</t>
+        </is>
+      </c>
+      <c r="AM21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN21" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AO21" s="3" t="inlineStr">
+        <is>
+          <t>L57-3</t>
+        </is>
+      </c>
+      <c r="AP21" s="3" t="inlineStr">
+        <is>
+          <t>85.34308</t>
+        </is>
+      </c>
+      <c r="AQ21" s="3" t="inlineStr"/>
+      <c r="AR21" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS21" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT21" s="3" t="inlineStr">
+        <is>
+          <t>2d 43m</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV21" s="3" t="inlineStr">
+        <is>
+          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AX21" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 5:03 PM</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>w7A8I7MXNVw6IhJoudC/TknnOVKMobUO</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Case</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>Update</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>WIFI6</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>TKT1380397</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Ale</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>Completed</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>Sunil Ale</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t>9803609995</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr"/>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:03:09 PM</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr"/>
+      <c r="T22" s="3" t="inlineStr"/>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>9803609995</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>27 Oct 2026 03:07:09 PM</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t>28 Oct 2026 05:03:09 PM</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="Y22" s="3" t="inlineStr">
+        <is>
+          <t>27.66715</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t>General / Other Issues</t>
+        </is>
+      </c>
+      <c r="AA22" s="3" t="inlineStr">
+        <is>
+          <t>Layer 1-User</t>
+        </is>
+      </c>
+      <c r="AB22" s="3" t="inlineStr">
+        <is>
+          <t>L1  Support</t>
+        </is>
+      </c>
+      <c r="AC22" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="AD22" s="3" t="inlineStr"/>
+      <c r="AE22" s="3" t="inlineStr">
+        <is>
+          <t>Ekantakuna lalitpur near Tibetan Laphing Center, Bagmati, Central, Nepal</t>
+        </is>
+      </c>
+      <c r="AF22" s="3" t="inlineStr"/>
+      <c r="AG22" s="3" t="inlineStr">
+        <is>
+          <t>Router Upgrade  Wi-Fi 6</t>
+        </is>
+      </c>
+      <c r="AH22" s="3" t="inlineStr"/>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>11:56 hour</t>
+        </is>
+      </c>
+      <c r="AJ22" s="3" t="inlineStr"/>
+      <c r="AK22" s="3" t="inlineStr"/>
+      <c r="AL22" s="3" t="inlineStr">
+        <is>
+          <t>Puja Khadka</t>
+        </is>
+      </c>
+      <c r="AM22" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AN22" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO22" s="3" t="inlineStr">
+        <is>
+          <t>2,10</t>
+        </is>
+      </c>
+      <c r="AP22" s="3" t="inlineStr">
+        <is>
+          <t>85.30986</t>
+        </is>
+      </c>
+      <c r="AQ22" s="3" t="inlineStr"/>
+      <c r="AR22" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AS22" s="3" t="inlineStr">
+        <is>
+          <t>0m</t>
+        </is>
+      </c>
+      <c r="AT22" s="3" t="inlineStr">
+        <is>
+          <t>1d 1h 56m</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr">
+        <is>
+          <t>Completed (Completed)</t>
+        </is>
+      </c>
+      <c r="AV22" s="3" t="inlineStr">
+        <is>
+          <t>Case : WIFI6  has been updated by Shashikant Chaudhary</t>
+        </is>
+      </c>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>WiFi 6 Upgrade</t>
+        </is>
+      </c>
+      <c r="AX22" s="3" t="inlineStr">
+        <is>
+          <t>Shashikant Chaudhary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
+++ b/EXECUTIVE_TEAM_AUDIT_REPORT_28_Oct_2026.xlsx
@@ -923,7 +923,7 @@
     <col width="27" customWidth="1" min="41" max="41"/>
     <col width="13" customWidth="1" min="42" max="42"/>
     <col width="17" customWidth="1" min="43" max="43"/>
-    <col width="45" customWidth="1" min="44" max="44"/>
+    <col width="34" customWidth="1" min="44" max="44"/>
     <col width="34" customWidth="1" min="45" max="45"/>
     <col width="33" customWidth="1" min="46" max="46"/>
     <col width="32" customWidth="1" min="47" max="47"/>
@@ -3821,10 +3821,8 @@
           <t>Digam Kumar Rana</t>
         </is>
       </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>9702683606</t>
-        </is>
+      <c r="O15" s="3" t="n">
+        <v>9702683606</v>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
@@ -3859,10 +3857,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y15" s="3" t="inlineStr">
-        <is>
-          <t>27.6553579</t>
-        </is>
+      <c r="Y15" s="3" t="n">
+        <v>27.6553579</v>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
@@ -3918,25 +3914,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN15" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN15" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
           <t>4,12</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>85.3559794</t>
-        </is>
+      <c r="AP15" s="3" t="n">
+        <v>85.3559794</v>
       </c>
       <c r="AQ15" s="3" t="inlineStr"/>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
@@ -4037,10 +4029,8 @@
           <t>Aayush shrestha</t>
         </is>
       </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>9843468465</t>
-        </is>
+      <c r="O16" s="3" t="n">
+        <v>9843468465</v>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
@@ -4075,10 +4065,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y16" s="3" t="inlineStr">
-        <is>
-          <t>27.67349</t>
-        </is>
+      <c r="Y16" s="3" t="n">
+        <v>27.67349</v>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
@@ -4130,25 +4118,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN16" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
           <t>L51-6</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>85.37342</t>
-        </is>
+      <c r="AP16" s="3" t="n">
+        <v>85.37342</v>
       </c>
       <c r="AQ16" s="3" t="inlineStr"/>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
@@ -4249,10 +4233,8 @@
           <t>Riwaz Thapa</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>9843819136</t>
-        </is>
+      <c r="O17" s="3" t="n">
+        <v>9843819136</v>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
@@ -4338,10 +4320,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN17" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
@@ -4352,7 +4332,7 @@
       <c r="AQ17" s="3" t="inlineStr"/>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
@@ -4453,10 +4433,8 @@
           <t>Anjali Khadka</t>
         </is>
       </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>9813192017</t>
-        </is>
+      <c r="O18" s="3" t="n">
+        <v>9813192017</v>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
@@ -4491,10 +4469,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y18" s="3" t="inlineStr">
-        <is>
-          <t>27.667993</t>
-        </is>
+      <c r="Y18" s="3" t="n">
+        <v>27.667993</v>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
@@ -4546,25 +4522,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN18" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
           <t>3,12</t>
         </is>
       </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>85.368072</t>
-        </is>
+      <c r="AP18" s="3" t="n">
+        <v>85.368072</v>
       </c>
       <c r="AQ18" s="3" t="inlineStr"/>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6 upgrade   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
@@ -4665,10 +4637,8 @@
           <t>Prashant Ulak</t>
         </is>
       </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>9861691382</t>
-        </is>
+      <c r="O19" s="3" t="n">
+        <v>9861691382</v>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
@@ -4703,10 +4673,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>27.6781</t>
-        </is>
+      <c r="Y19" s="3" t="n">
+        <v>27.6781</v>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
@@ -4758,25 +4726,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN19" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>85.34772</t>
-        </is>
+      <c r="AP19" s="3" t="n">
+        <v>85.34772</v>
       </c>
       <c r="AQ19" s="3" t="inlineStr"/>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>Case : wifi6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
@@ -4877,10 +4841,8 @@
           <t>Anurag Karki</t>
         </is>
       </c>
-      <c r="O20" s="3" t="inlineStr">
-        <is>
-          <t>9861095557</t>
-        </is>
+      <c r="O20" s="3" t="n">
+        <v>9861095557</v>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
@@ -4970,10 +4932,8 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN20" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN20" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO20" s="3" t="inlineStr">
         <is>
@@ -4984,7 +4944,7 @@
       <c r="AQ20" s="3" t="inlineStr"/>
       <c r="AR20" s="3" t="inlineStr">
         <is>
-          <t>Case : Wifi 6   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS20" s="3" t="inlineStr">
@@ -5085,10 +5045,8 @@
           <t>Ramesh Kumar Regmi</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
-        <is>
-          <t>9811566677</t>
-        </is>
+      <c r="O21" s="3" t="n">
+        <v>9811566677</v>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
@@ -5123,10 +5081,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y21" s="3" t="inlineStr">
-        <is>
-          <t>27.69851</t>
-        </is>
+      <c r="Y21" s="3" t="n">
+        <v>27.69851</v>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
@@ -5182,25 +5138,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN21" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="AN21" s="3" t="n">
+        <v>6</v>
       </c>
       <c r="AO21" s="3" t="inlineStr">
         <is>
           <t>L57-3</t>
         </is>
       </c>
-      <c r="AP21" s="3" t="inlineStr">
-        <is>
-          <t>85.34308</t>
-        </is>
+      <c r="AP21" s="3" t="n">
+        <v>85.34308</v>
       </c>
       <c r="AQ21" s="3" t="inlineStr"/>
       <c r="AR21" s="3" t="inlineStr">
         <is>
-          <t>Case : router change   has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS21" s="3" t="inlineStr">
@@ -5301,10 +5253,8 @@
           <t>Sunil Ale</t>
         </is>
       </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>9803609995</t>
-        </is>
+      <c r="O22" s="3" t="n">
+        <v>9803609995</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
@@ -5339,10 +5289,8 @@
           <t>Active</t>
         </is>
       </c>
-      <c r="Y22" s="3" t="inlineStr">
-        <is>
-          <t>27.66715</t>
-        </is>
+      <c r="Y22" s="3" t="n">
+        <v>27.66715</v>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
@@ -5394,25 +5342,21 @@
           <t>Shashikant Chaudhary</t>
         </is>
       </c>
-      <c r="AN22" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="AN22" s="3" t="n">
+        <v>4</v>
       </c>
       <c r="AO22" s="3" t="inlineStr">
         <is>
           <t>2,10</t>
         </is>
       </c>
-      <c r="AP22" s="3" t="inlineStr">
-        <is>
-          <t>85.30986</t>
-        </is>
+      <c r="AP22" s="3" t="n">
+        <v>85.30986</v>
       </c>
       <c r="AQ22" s="3" t="inlineStr"/>
       <c r="AR22" s="3" t="inlineStr">
         <is>
-          <t>Case : WIFI6  has been updated by Shashikant Chaudhary</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="AS22" s="3" t="inlineStr">
